--- a/1_Dog.M0_WGS/Article_Figures/Supplementary Table S2.xlsx
+++ b/1_Dog.M0_WGS/Article_Figures/Supplementary Table S2.xlsx
@@ -457,31 +457,31 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>189431</v>
+        <v>3145625</v>
       </c>
       <c r="C3" t="n">
-        <v>163784737</v>
+        <v>3948109978</v>
       </c>
       <c r="D3" t="n">
-        <v>864.614223648716</v>
+        <v>1255.11145734154</v>
       </c>
       <c r="E3" t="n">
-        <v>521</v>
+        <v>590</v>
       </c>
       <c r="F3" t="n">
-        <v>1115</v>
+        <v>2514</v>
       </c>
       <c r="G3" t="n">
-        <v>15.2741263098437</v>
+        <v>30.4719281016968</v>
       </c>
       <c r="H3" t="n">
-        <v>15.1612</v>
+        <v>31.809</v>
       </c>
       <c r="I3" t="n">
-        <v>35.5211</v>
+        <v>44.6255</v>
       </c>
       <c r="J3" t="n">
-        <v>10.773</v>
+        <v>4.7742</v>
       </c>
     </row>
   </sheetData>
